--- a/docs/downloads/Aurora.xlsx
+++ b/docs/downloads/Aurora.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D562"/>
+  <dimension ref="A1:D560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Raney</t>
+          <t>Lynn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Hashinsky</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>raneyng@gmail.com</t>
+          <t>lyhash62@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lynn</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hashinsky</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lyhash62@gmail.com</t>
+          <t>jcwcellfung@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -587,19 +587,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jcwcellfung@gmail.com</t>
+          <t>linyongzhong@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -609,11 +601,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Danny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wong</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>linyongzhong@gmail.com</t>
+          <t>dannytwong@gnail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -625,17 +625,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Behnaz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Pirmoradi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dannytwong@gnail.com</t>
+          <t>behnazpirmoradi@yahoo.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -647,17 +647,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Behnaz</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pirmoradi</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>behnazpirmoradi@yahoo.com</t>
+          <t>wv1111yolo@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -669,17 +669,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>First</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wv1111yolo@gmail.com</t>
+          <t>firstname@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -691,17 +691,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Lorry</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Dezorzi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>firstname@gmail.com</t>
+          <t>lorrydezorzi4@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lorry</t>
+          <t>Shelley</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dezorzi</t>
+          <t>Macdougall</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lorrydezorzi4@gmail.com</t>
+          <t>shelleymacd@icloud.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -733,19 +733,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Shelley</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Macdougall</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>shelleymacd@icloud.com</t>
+          <t>renee_sang@hotmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -755,11 +747,19 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Depass</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>renee_sang@hotmail.com</t>
+          <t>annadep2872@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -771,17 +771,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Depass</t>
+          <t>Albino</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>annadep2872@gmail.com</t>
+          <t>cathyalbino3@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Albino</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cathyalbino3@gmail.com</t>
+          <t>jaidevpatel318@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -813,19 +813,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Jay</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jaidevpatel318@gmail.com</t>
+          <t>lorimerclub@icloud.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -835,11 +827,19 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rozmine</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lorimerclub@icloud.com</t>
+          <t>rozminem@rogers.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -851,17 +851,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rozmine</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Cormacchia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rozminem@rogers.com</t>
+          <t>amanda//@momminginc.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -873,19 +873,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yan</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gu</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>guniuniu2002@hotmail.com</t>
-        </is>
-      </c>
+          <t>Tse</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -895,19 +891,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cormacchia</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>amanda//@momminginc.com</t>
-        </is>
-      </c>
+          <t>Fung</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -917,15 +909,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tse</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Bakhshi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>bakhshibon@yahoo.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -935,15 +931,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Chui</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fung</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ctwborg@gmail.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -953,17 +953,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kimberly</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bakhshi</t>
+          <t>Van Praagh</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bakhshibon@yahoo.com</t>
+          <t>kimberlyvpis@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -975,19 +975,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chui</t>
+          <t>Dmitri</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ctwborg@gmail.com</t>
-        </is>
-      </c>
+          <t>Minkin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -997,19 +993,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kimberly</t>
+          <t>Ayan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Van Praagh</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>kimberlyvpis@gmail.com</t>
-        </is>
-      </c>
+          <t>Prabhakar (Tina)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -1019,12 +1011,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dmitri</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Minkin</t>
+          <t>Prabhakar (Tina)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1037,15 +1029,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ayan</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Prabhakar (Tina)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Poncelet</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kaitlyn@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -1055,12 +1051,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prabhakar (Tina)</t>
+          <t>Kong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1073,19 +1069,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Liza</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Poncelet</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>kaitlyn@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -1095,12 +1087,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kong</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1113,12 +1105,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Liza</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Na</t>
+          <t>Rabinowitz</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1131,7 +1123,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Macy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1149,12 +1141,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>PAK HEI PETRUS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rabinowitz</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1167,12 +1159,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Macy</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Ren</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1185,12 +1177,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PAK HEI PETRUS</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1203,12 +1195,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ren</t>
+          <t>Quach</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1221,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Quach</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1239,12 +1231,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1257,12 +1249,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Taya</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Arellano</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1275,12 +1267,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1293,12 +1285,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Taya</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arellano</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1311,12 +1303,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Arellano</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1329,12 +1321,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Kwok</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1347,12 +1339,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Arellano</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1365,12 +1357,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kwok</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1383,12 +1375,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Raso</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1401,12 +1393,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Arellano</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1419,12 +1411,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Raso</t>
+          <t>Tram Ha</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1437,12 +1429,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Arellano</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1455,12 +1447,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Kazjmier</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tram Ha</t>
+          <t>Bieniak</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1473,12 +1465,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Yung</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1491,12 +1483,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kazjmier</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bieniak</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1509,12 +1501,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>George Jr.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yung</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1527,12 +1519,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1545,12 +1537,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>George Jr.</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Zelko</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1563,12 +1555,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Micheal</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Zelko</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1581,12 +1573,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Edmund</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Zelko</t>
+          <t>Kwong</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1599,12 +1591,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Micheal</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Zelko</t>
+          <t>Heron</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1617,12 +1609,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Edmund</t>
+          <t>Okran</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kwong</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1635,12 +1627,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Manni</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Heron</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1653,12 +1645,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Okran</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Mazza</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1671,12 +1663,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Manni</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Yip</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1689,12 +1681,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mazza</t>
+          <t>LEVANDOVSKY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1707,12 +1699,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1725,12 +1717,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LEVANDOVSKY</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1743,12 +1735,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yee</t>
+          <t>Ting</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1761,12 +1753,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1779,12 +1771,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ting</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1797,12 +1789,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1815,12 +1807,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1833,12 +1825,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Ada</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1851,12 +1843,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Xiao</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1869,12 +1861,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ada</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Zou</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1887,12 +1879,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Xiao</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1905,12 +1897,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1923,12 +1915,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Lalique K Y</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1941,12 +1933,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Rocky</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1959,12 +1951,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lalique K Y</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Sin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1977,12 +1969,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Zev</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Desa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1995,12 +1987,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sin</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2013,12 +2005,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Zev</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Desa</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2031,12 +2023,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Zimo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2049,12 +2041,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2067,12 +2059,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Zimo</t>
+          <t>Aileen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2085,12 +2077,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Linh MK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Ha</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2103,12 +2095,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Aileen</t>
+          <t>Dickson</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Lau</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2121,12 +2113,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Linh MK</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ha</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2139,12 +2131,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dickson</t>
+          <t>Jingqi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lau</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2157,12 +2149,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Ilene</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Trieu</t>
+          <t>Hoang</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2175,12 +2167,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jingqi</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2193,12 +2185,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ilene</t>
+          <t>Chapman</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hoang</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2211,12 +2203,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Yee</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2229,12 +2221,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chapman</t>
+          <t>Darren</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Dim</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2247,7 +2239,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2265,12 +2257,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Darren</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dim</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2283,12 +2275,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2301,12 +2293,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2319,12 +2311,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Fayth</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Trieu</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2337,12 +2329,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2355,7 +2347,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Fayth</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2373,12 +2365,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Trieu</t>
+          <t>Ha</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2391,12 +2383,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>So</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2409,12 +2401,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ha</t>
+          <t>Cheng</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2427,12 +2419,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>So</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2445,12 +2437,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cheng</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2463,12 +2455,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2481,12 +2473,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Tony K K</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Mok</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2499,12 +2491,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trieu</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2517,12 +2509,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tony K K</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mok</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2535,12 +2527,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Rocco</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Mazza</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2553,12 +2545,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Robbie</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2571,12 +2563,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Rocco</t>
+          <t>Rocky</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mazza</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2589,12 +2581,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Robbie</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Zhao</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2607,12 +2599,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2625,12 +2617,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Zhao</t>
+          <t>Cheung</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2643,12 +2635,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2661,12 +2653,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2679,12 +2671,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Xin</t>
+          <t>Domenic</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Mazza</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2697,12 +2689,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2715,12 +2707,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Domenic</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mazza</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2733,12 +2725,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>Ariel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Strugach</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2751,12 +2743,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2769,12 +2761,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Strugach</t>
+          <t>Malik</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2787,12 +2779,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Kunyang</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2805,12 +2797,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Malik</t>
+          <t>Ching</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2823,12 +2815,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kunyang</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Hoang</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2841,12 +2833,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ching</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2859,12 +2851,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Hoang</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2877,12 +2869,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2895,12 +2887,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Yuk</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2913,12 +2905,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2931,12 +2923,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Yuk</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2949,12 +2941,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jeffrey</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2967,12 +2959,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2985,12 +2977,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jeffrey</t>
+          <t>Hanzi</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3003,12 +2995,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Noime</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Manalo</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3021,12 +3013,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Hanzi</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Kwok</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3039,12 +3031,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Noime</t>
+          <t>Lucinda</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Manalo</t>
+          <t>Shum</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3057,12 +3049,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kwok</t>
+          <t>Ting</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3075,12 +3067,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lucinda</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Shum</t>
+          <t>Auyang</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3093,12 +3085,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ting</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3111,12 +3103,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Auyang</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3129,12 +3121,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3147,12 +3139,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3165,12 +3157,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Mazza</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3183,12 +3175,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Trieu</t>
+          <t>Maclean</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3201,12 +3193,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Ashton</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mazza</t>
+          <t>Byard</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3219,12 +3211,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Maclean</t>
+          <t>Vena</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3237,12 +3229,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ashton</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Byard</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3255,12 +3247,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vena</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3273,12 +3265,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3291,12 +3283,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>zita</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3309,12 +3301,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Vena</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3327,12 +3319,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>zita</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3345,12 +3337,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Vena</t>
+          <t>Perna</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3363,12 +3355,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Byard</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3381,12 +3373,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Perna</t>
+          <t>Pennant</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3399,15 +3391,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Byard</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>Turchi</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>helen.turchi@hotmail.com</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3417,12 +3413,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Pennant</t>
+          <t>Tsang</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3435,19 +3431,15 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Turchi</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>helen.turchi@hotmail.com</t>
-        </is>
-      </c>
+          <t>Turgeon</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3457,12 +3449,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Tsang</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3475,12 +3467,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Turgeon</t>
+          <t>Abuan</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3493,12 +3485,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Pennant</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3511,15 +3503,19 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Amin</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Abuan</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>Jutha</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>amin.jutha@gmail.com</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3529,15 +3525,19 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Lyka</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Pennant</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>Dinglass</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>lyka.dinglass0511@gmail.com</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3547,19 +3547,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Amin</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Jutha</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>amin.jutha@gmail.com</t>
-        </is>
-      </c>
+          <t>Hon</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3569,19 +3565,15 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Lyka</t>
+          <t>Chi Wai</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dinglass</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>lyka.dinglass0511@gmail.com</t>
-        </is>
-      </c>
+          <t>Tsang</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3591,15 +3583,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Flavio</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Hon</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>Turchi</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>flaviotuchni626@gmaill.com</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3609,15 +3605,19 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Chi Wai</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tsang</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>Chang</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>dongpingzheng@me.com</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3627,17 +3627,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Flavio</t>
+          <t>Nian Qi</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Turchi</t>
+          <t>Bei</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>flaviotuchni626@gmaill.com</t>
+          <t>minqie@yahoo.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3649,19 +3649,15 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Calix</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Chang</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>dongpingzheng@me.com</t>
-        </is>
-      </c>
+          <t>Tsang</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3671,17 +3667,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Nian Qi</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bei</t>
+          <t>Sarracini</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>minqie@yahoo.com</t>
+          <t>christian.sarracini@outlook.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3693,12 +3689,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Calix</t>
+          <t>Ridley</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tsang</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3711,19 +3707,15 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sarracini</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>christian.sarracini@outlook.com</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3733,12 +3725,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ridley</t>
+          <t>Imran</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Rhemtulla</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3751,12 +3743,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Noorie</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Samji</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3769,12 +3761,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Imran</t>
+          <t>Shamez</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Rhemtulla</t>
+          <t>Bachoo</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3787,12 +3779,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Noorie</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Samji</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -3805,12 +3797,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Shamez</t>
+          <t>Mustafa</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Bachoo</t>
+          <t>Kamalia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -3823,12 +3815,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dhanji</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -3841,12 +3833,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Mustafa</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Kamalia</t>
+          <t>Dhanji</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -3859,12 +3851,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dhanji</t>
+          <t>Joo</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -3877,12 +3869,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Kaylyn</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dhanji</t>
+          <t>Diao</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -3895,15 +3887,19 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Fawzat</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Joo</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>Zawadi</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>fawzatzawadi23@gmail.com</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3913,12 +3909,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Kaylyn</t>
+          <t>Darya</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Diao</t>
+          <t>Oleynik</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -3931,17 +3927,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Fawzat</t>
+          <t>Sakina</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Zawadi</t>
+          <t>Gulamali</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>fawzatzawadi23@gmail.com</t>
+          <t>313homeschoolers@gmail.com</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -3953,15 +3949,19 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Darya</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Oleynik</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
+          <t>Huynh</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>amy.h.53@hotmail.com</t>
+        </is>
+      </c>
       <c r="D190" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -3971,17 +3971,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Sakina</t>
+          <t>cooper</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gulamali</t>
+          <t>turgeon</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>313homeschoolers@gmail.com</t>
+          <t>melsmth_366@hotmail.com</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -3993,19 +3993,15 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Huynh</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>amy.h.53@hotmail.com</t>
-        </is>
-      </c>
+          <t>Diao</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4015,19 +4011,15 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>cooper</t>
+          <t>Makena</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>turgeon</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>melsmth_366@hotmail.com</t>
-        </is>
-      </c>
+          <t>Faria</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4037,12 +4029,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>Yelena</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Diao</t>
+          <t>Vassilyeva</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4055,15 +4047,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Makena</t>
+          <t>johanna</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Faria</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>apollinaro</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>johannarosegreco@gmail.com</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4073,12 +4069,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Yelena</t>
+          <t>Daegan</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Vassilyeva</t>
+          <t>Sit</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4091,17 +4087,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>johanna</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>apollinaro</t>
+          <t>Apollinaro</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>johannarosegreco@gmail.com</t>
+          <t>johnapollinaro@gmail.com</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4113,12 +4109,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Daegan</t>
+          <t>Abigail</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sit</t>
+          <t>Tse</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4131,17 +4127,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Apollinaro</t>
+          <t>Passy</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>johnapollinaro@gmail.com</t>
+          <t>jpassrelli@rogers.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4153,7 +4149,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4171,17 +4167,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Qais</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Passy</t>
+          <t>Alibhai</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>jpassrelli@rogers.com</t>
+          <t>qaisalibhai@gmail.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4193,15 +4189,19 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Tse</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
+          <t>Chartier</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>eric.a.chartier01@gmail.com</t>
+        </is>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4211,17 +4211,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Qais</t>
+          <t>shannon</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Alibhai</t>
+          <t>quinn</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>qaisalibhai@gmail.com</t>
+          <t>shannquinn1@gmail.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4233,19 +4233,15 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Chartier</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>eric.a.chartier01@gmail.com</t>
-        </is>
-      </c>
+          <t>Oleynik</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4255,19 +4251,15 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>shannon</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>quinn</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>shannquinn1@gmail.com</t>
-        </is>
-      </c>
+          <t>Oleynik</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4277,15 +4269,19 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Oleynik</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>Pak</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>paknsam285@gmail.com</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4295,15 +4291,19 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Marc</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Oleynik</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
+          <t>chartier</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>marcc1632@gmail.com</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4313,19 +4313,15 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Pak</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>paknsam285@gmail.com</t>
-        </is>
-      </c>
+          <t>Tse</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4335,17 +4331,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Giancarlo</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>chartier</t>
+          <t>Gallucci</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>marcc1632@gmail.com</t>
+          <t>giancarlo.l.gallucci@gmail.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4357,15 +4353,19 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Zaid</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Tse</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>Jurji</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>zaidjurji@yahoo.com</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4375,19 +4375,15 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Giancarlo</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Gallucci</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>giancarlo.l.gallucci@gmail.com</t>
-        </is>
-      </c>
+          <t>Vander Leeuw</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4397,19 +4393,15 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Zaid</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Jurji</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>zaidjurji@yahoo.com</t>
-        </is>
-      </c>
+          <t>Mehew</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4419,12 +4411,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Briana</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Vander Leeuw</t>
+          <t>Vander leeuw</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4437,15 +4429,19 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mehew</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>Yu</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>yttharper@gmail.com</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4455,12 +4451,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vander leeuw</t>
+          <t>Mehew</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4473,19 +4469,15 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Aidan</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>yttharper@gmail.com</t>
-        </is>
-      </c>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4495,12 +4487,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mehew</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4513,12 +4505,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Aidan</t>
+          <t>Nixon</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Mehew</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4531,12 +4523,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Lanie</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4549,12 +4541,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>Hilda</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Mehew</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4567,7 +4559,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Lanie</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4585,12 +4577,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Hilda</t>
+          <t>Davide</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Bianchi</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4603,12 +4595,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Amin</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Zamanifar</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4621,12 +4613,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Davide</t>
+          <t>Jaydan</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Bianchi</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4639,12 +4631,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Amin</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Zamanifar</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4657,12 +4649,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Jaydan</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Bianchi</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4675,12 +4667,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Sidra</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Shaik</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4693,12 +4685,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Bianchi</t>
+          <t>Vander Leeuw</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4711,12 +4703,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sidra</t>
+          <t>Yannes</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Shaik</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4729,12 +4721,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Vander Leeuw</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4747,15 +4739,19 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Yannes</t>
+          <t>Katreena</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Tang</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>katreena.huang@gmail.com</t>
+        </is>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4765,12 +4761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4783,19 +4779,15 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Katreena</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>katreena.huang@gmail.com</t>
-        </is>
-      </c>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4805,15 +4797,19 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
+          <t>Commisso</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>isabella.commisso86@gmail.com</t>
+        </is>
+      </c>
       <c r="D234" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4823,12 +4819,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Yip</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -4841,19 +4837,15 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Babak</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Commisso</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>isabella.commisso86@gmail.com</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4863,12 +4855,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Sanny</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>Kong</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -4881,12 +4873,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Babak</t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -4899,15 +4891,19 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Sanny</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Kong</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
+          <t>Zhaang</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>jollin.carol1988@gmail.com</t>
+        </is>
+      </c>
       <c r="D239" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4917,15 +4913,19 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Han</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ellie.wang1129@gmail.com</t>
+        </is>
+      </c>
       <c r="D240" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4935,19 +4935,15 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Zhaang</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>jollin.carol1988@gmail.com</t>
-        </is>
-      </c>
+          <t>Yip</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4957,17 +4953,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>maria</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Kostiounina</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ellie.wang1129@gmail.com</t>
+          <t>mk.ostiounina@gmail.com</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -4979,15 +4975,19 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Yip</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>Koshkaryan</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>albertkoshaaryan@gmail.com</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -4997,17 +4997,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>maria</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kostiounina</t>
+          <t>Chang</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>mk.ostiounina@gmail.com</t>
+          <t>royc0108@yahoo.com</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5019,19 +5019,15 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Koshkaryan</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>albertkoshaaryan@gmail.com</t>
-        </is>
-      </c>
+          <t>yip</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5041,19 +5037,15 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Chang</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>royc0108@yahoo.com</t>
-        </is>
-      </c>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5063,15 +5055,19 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>nicholas</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>yip</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
+          <t>solimena</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>nicksolimena17@gmail.com</t>
+        </is>
+      </c>
       <c r="D247" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5081,12 +5077,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Josie</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Scali</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5099,19 +5095,15 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>nicholas</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>solimena</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>nicksolimena17@gmail.com</t>
-        </is>
-      </c>
+          <t>Wan</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5121,12 +5113,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Josie</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Scali</t>
+          <t>Sav</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5139,12 +5131,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Wan</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5157,12 +5149,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Sav</t>
+          <t>Kwok</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5175,12 +5167,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Teagan</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5193,12 +5185,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Bella</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Kwok</t>
+          <t>Mroz</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5211,12 +5203,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Teagan</t>
+          <t>Candra</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5229,12 +5221,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Bella</t>
+          <t>Thai</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Mroz</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5247,12 +5239,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Candra</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Hutton</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5265,12 +5257,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Thai</t>
+          <t>Rhian</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Zhao</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5283,12 +5275,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Shalina</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>Jessa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5301,12 +5293,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Rhian</t>
+          <t>Emmy</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Zhao</t>
+          <t>Cuello</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5319,12 +5311,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Shalina</t>
+          <t>Ye</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Jessa</t>
+          <t>Yan</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5337,12 +5329,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Emmy</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Cuello</t>
+          <t>Hua</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5355,12 +5347,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Ye</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Yan</t>
+          <t>Choi</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5373,12 +5365,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Hua</t>
+          <t>Cuello</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5391,12 +5383,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Kaydon</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Zhao</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5409,12 +5401,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Cuello</t>
+          <t>Hosang</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5427,12 +5419,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Kaydon</t>
+          <t>Layla</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Zhao</t>
+          <t>Hutton</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5445,12 +5437,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Jaxon</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Hosang</t>
+          <t>mroz</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5463,12 +5455,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Layla</t>
+          <t>Washon</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>Gow</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5481,12 +5473,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Jaxon</t>
+          <t>Lauryn</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>mroz</t>
+          <t>Hosang</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5499,12 +5491,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Washon</t>
+          <t>Murtaza</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Gow</t>
+          <t>Jessa</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5517,12 +5509,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Lauryn</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Hosang</t>
+          <t>Mroz</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5535,15 +5527,19 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Murtaza</t>
+          <t>Cassandra</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Jessa</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
+          <t>Cugalj</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>cassiej@rogers.com</t>
+        </is>
+      </c>
       <c r="D273" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5553,15 +5549,19 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>April</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Mroz</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr"/>
+          <t>Cugalj</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>april.cugalj@gmail.com</t>
+        </is>
+      </c>
       <c r="D274" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5571,17 +5571,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Cassandra</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Cugalj</t>
+          <t>Cormacchia</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>cassiej@rogers.com</t>
+          <t>amanda/@momminginc.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -5593,19 +5593,15 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Svetlana</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Cugalj</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>april.cugalj@gmail.com</t>
-        </is>
-      </c>
+          <t>Rassolova</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5615,19 +5611,15 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Cormacchia</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>amanda/@momminginc.com</t>
-        </is>
-      </c>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5637,12 +5629,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Svetlana</t>
+          <t>Casilia</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Rassolova</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5655,15 +5647,19 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
+          <t>Watts</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>hudsondpwatts@gmail.com</t>
+        </is>
+      </c>
       <c r="D279" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5673,12 +5669,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Casilia</t>
+          <t>Gideon</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Mak</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5691,19 +5687,15 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Watts</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>hudsondpwatts@gmail.com</t>
-        </is>
-      </c>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5713,15 +5705,19 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Gideon</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Mak</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr"/>
+          <t>Keall</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>mia@keall.com</t>
+        </is>
+      </c>
       <c r="D282" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5731,12 +5727,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Jianjie</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Ling</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -5749,17 +5745,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Keall</t>
+          <t>Watts</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>mia@keall.com</t>
+          <t>jeremyprwatts@gmail.com</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -5771,12 +5767,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Jianjie</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Ling</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -5789,17 +5785,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Caitlyn</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Watts</t>
+          <t>Swarbrick</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>jeremyprwatts@gmail.com</t>
+          <t>caitlyn_swarb@gmail.com</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -5811,12 +5807,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -5829,17 +5825,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Caitlyn</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Swarbrick</t>
+          <t>Cugalj</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>caitlyn_swarb@gmail.com</t>
+          <t>sabrina.cugalj@gmail.com</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -5851,12 +5847,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -5869,19 +5865,15 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cugalj</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>sabrina.cugalj@gmail.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5891,15 +5883,19 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Caitlyn</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr"/>
+          <t>Swarbrick</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>amanda_stead@hotmail.com</t>
+        </is>
+      </c>
       <c r="D291" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5909,15 +5905,19 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Nuslin</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr"/>
+          <t>Huda</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>m1naz@yahoo.com</t>
+        </is>
+      </c>
       <c r="D292" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5927,19 +5927,15 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Caitlyn</t>
+          <t>SATISH</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Swarbrick</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>amanda_stead@hotmail.com</t>
-        </is>
-      </c>
+          <t>KUMAR</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5949,19 +5945,15 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Nuslin</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Huda</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>m1naz@yahoo.com</t>
-        </is>
-      </c>
+          <t>Poole</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -5971,12 +5963,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SATISH</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -5989,15 +5981,19 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Hui</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Poole</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>wanghuima@gmail.ca</t>
+        </is>
+      </c>
       <c r="D296" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6007,12 +6003,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Cheng</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -6025,19 +6021,15 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Hui</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>wanghuima@gmail.ca</t>
-        </is>
-      </c>
+          <t>Herod</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6047,12 +6039,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Cheng</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -6065,15 +6057,19 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Satish</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Herod</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
+          <t>Kumar</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>satish.kumar2@hpe.com</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6083,12 +6079,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6101,19 +6097,15 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Satish</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Kumar</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>satish.kumar2@hpe.com</t>
-        </is>
-      </c>
+          <t>Poole</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6123,12 +6115,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Jing</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6141,15 +6133,19 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Anuja</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Poole</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>anuja.sharma@rogers.com</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6159,12 +6155,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Jing</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -6177,19 +6173,15 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Anuja</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>anuja.sharma@rogers.com</t>
-        </is>
-      </c>
+          <t>Bachoo</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6199,12 +6191,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6217,12 +6209,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Massimo</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Bachoo</t>
+          <t>Spagnuolo</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6235,12 +6227,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Luciano</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Spagnuolo</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6253,15 +6245,19 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Massimo</t>
+          <t>Arif</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Spagnuolo</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr"/>
+          <t>Ratansi</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>aratansi@bseen.com</t>
+        </is>
+      </c>
       <c r="D310" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6271,12 +6267,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Luciano</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Spagnuolo</t>
+          <t>Eichler</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6289,17 +6285,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Arif</t>
+          <t>Walter</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ratansi</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>aratansi@bseen.com</t>
+          <t>acelima1962@gmail.com</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6311,12 +6307,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Graeme</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Eichler</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6329,19 +6325,15 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Walter</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lima</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>acelima1962@gmail.com</t>
-        </is>
-      </c>
+          <t>Burgess</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -6351,12 +6343,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Graeme</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6369,12 +6361,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6387,12 +6379,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Aisling</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Ferris</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6405,12 +6397,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Brendan</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Ferris</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6423,12 +6415,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Aisling</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Ferris</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6441,12 +6433,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Brendan</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Ferris</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -6459,12 +6451,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Kwan</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6477,12 +6469,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Princeton</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>phillip</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -6495,12 +6487,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Liyanah</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Kwan</t>
+          <t>Zamir</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6513,12 +6505,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Princeton</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>phillip</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -6531,12 +6523,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Liyanah</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Zamir</t>
+          <t>phillip</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6549,12 +6541,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Audrina</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -6567,12 +6559,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>phillip</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6585,7 +6577,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Audrina</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -6603,12 +6595,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Servideo</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -6621,12 +6613,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>phillip</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -6639,12 +6631,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Aveline</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Servideo</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -6657,12 +6649,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>phillip</t>
+          <t>Hum</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -6675,12 +6667,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Aveline</t>
+          <t>Cameron</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -6693,12 +6685,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Hum</t>
+          <t>Faria</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -6711,12 +6703,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Cameron</t>
+          <t>Lucus</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -6729,12 +6721,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Brayden</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Faria</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -6747,12 +6739,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Lucus</t>
+          <t>Annalise</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Maugeri</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -6765,12 +6757,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Brayden</t>
+          <t>Lyss</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Arde</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -6783,12 +6775,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Annalise</t>
+          <t>Lola</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Maugeri</t>
+          <t>Yuan</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -6801,12 +6793,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Lyss</t>
+          <t>Natalie</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Arde</t>
+          <t>Maugeri</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -6819,12 +6811,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Lola</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Yuan</t>
+          <t>Lau</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -6837,12 +6829,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Ev</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Maugeri</t>
+          <t>Arde</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -6855,12 +6847,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lau</t>
+          <t>Hambly Millar</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -6873,7 +6865,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ev</t>
+          <t>Cris</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6891,12 +6883,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Hambly Millar</t>
+          <t>Tse</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -6909,12 +6901,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Cris</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Arde</t>
+          <t>Shum</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -6927,12 +6919,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Nikita</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Tse</t>
+          <t>Yermolenko</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -6945,12 +6937,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Shum</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -6963,12 +6955,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Yermolenko</t>
+          <t>Stern</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -6981,12 +6973,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Moschetti</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -6999,12 +6991,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Pieter</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Stern</t>
+          <t>Gouws</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -7017,12 +7009,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Moschetti</t>
+          <t>Kwok</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -7035,12 +7027,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Pieter</t>
+          <t>Ved</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Gouws</t>
+          <t>Ramphal</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -7053,12 +7045,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Kwok</t>
+          <t>Gouws</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -7071,12 +7063,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ved</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Ramphal</t>
+          <t>chan</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -7089,12 +7081,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>brandon</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Gouws</t>
+          <t>To</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -7107,15 +7099,19 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Colleen</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>chan</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr"/>
+          <t>Davey</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>collendavey@hotmail.com</t>
+        </is>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7125,12 +7121,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>brandon</t>
+          <t>Sabastian</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>To</t>
+          <t>chan</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -7143,19 +7139,15 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Colleen</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Davey</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>collendavey@hotmail.com</t>
-        </is>
-      </c>
+          <t>Gee</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7165,12 +7157,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Sabastian</t>
+          <t>Ka Wai</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>chan</t>
+          <t>Cheung</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -7183,12 +7175,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Anky</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Gee</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -7201,12 +7193,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ka Wai</t>
+          <t>Andrew E</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
@@ -7219,12 +7211,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Anky</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -7237,12 +7229,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Andrew E</t>
+          <t>Myra</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Ha</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -7255,12 +7247,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Trieu</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -7273,12 +7265,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Myra</t>
+          <t>Kezia</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Ha</t>
+          <t>Holden</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -7291,12 +7283,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Kiyaan</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -7309,12 +7301,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Kezia</t>
+          <t>Samaay</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Holden</t>
+          <t>Shewaramani</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -7327,12 +7319,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kiyaan</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -7345,12 +7337,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Samaay</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Shewaramani</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -7363,12 +7355,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Everly</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Lacroix</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -7381,12 +7373,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -7399,12 +7391,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Everly</t>
+          <t>Siwon</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lacroix</t>
+          <t>Choi</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -7417,12 +7409,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -7435,12 +7427,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Siwon</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Lacroix</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -7453,12 +7445,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -7471,12 +7463,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lacroix</t>
+          <t>Adamopoulos</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -7489,12 +7481,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Cameron</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Kivisto</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -7507,12 +7499,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Adamopoulos</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -7525,12 +7517,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Cameron</t>
+          <t>Lesley</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Kivisto</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -7543,12 +7535,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Alpesh</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
@@ -7561,12 +7553,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Lesley</t>
+          <t>Thimo</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Adamopoulos</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -7579,12 +7571,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Alpesh</t>
+          <t>Abbie</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Madill</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -7597,12 +7589,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Thimo</t>
+          <t>Tas</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Adamopoulos</t>
+          <t>mohamed</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
@@ -7615,7 +7607,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Abbie</t>
+          <t>Marlie</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -7633,12 +7625,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Tas</t>
+          <t>Adalyn</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>mohamed</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -7651,12 +7643,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Marlie</t>
+          <t>Suzi</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Madill</t>
+          <t>Flynn</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
@@ -7669,15 +7661,19 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Adalyn</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr"/>
+          <t>tang</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>jtang9121@gmail.com</t>
+        </is>
+      </c>
       <c r="D388" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7687,15 +7683,19 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Suzi</t>
+          <t>MIchael</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Flynn</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr"/>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>gbbts30000@outlook.com</t>
+        </is>
+      </c>
       <c r="D389" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7705,19 +7705,15 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>tang</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>jtang9121@gmail.com</t>
-        </is>
-      </c>
+          <t>Cheung</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7727,7 +7723,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>MIchael</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7735,11 +7731,7 @@
           <t>Chan</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>gbbts30000@outlook.com</t>
-        </is>
-      </c>
+      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7749,12 +7741,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Giovinazzo</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
@@ -7767,12 +7759,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Amar</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Atwal</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
@@ -7785,12 +7777,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Giovinazzo</t>
+          <t>Liang</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
@@ -7803,15 +7795,19 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Amar</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Atwal</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr"/>
+          <t>Muir</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>jimmymuir@rogers.com</t>
+        </is>
+      </c>
       <c r="D395" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7821,15 +7817,19 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jakob</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Liang</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr"/>
+          <t>Vrankovic</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>jakobvranko@gmail.com</t>
+        </is>
+      </c>
       <c r="D396" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7839,19 +7839,15 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Yash</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Muir</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>jimmymuir@rogers.com</t>
-        </is>
-      </c>
+          <t>Atwal</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7861,17 +7857,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Jakob</t>
+          <t>athena</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Vrankovic</t>
+          <t>woo</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>jakobvranko@gmail.com</t>
+          <t>andywoo23+@gmail.com</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -7883,15 +7879,19 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Yash</t>
+          <t>august</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Atwal</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr"/>
+          <t>woo</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>andywoo23-@gmail.com</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7901,19 +7901,15 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>athena</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>woo</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>andywoo23+@gmail.com</t>
-        </is>
-      </c>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7923,19 +7919,15 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>august</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>woo</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>andywoo23-@gmail.com</t>
-        </is>
-      </c>
+          <t>Mayorova</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -7945,12 +7937,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Prabhakar</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
@@ -7963,12 +7955,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Kishore</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Mayorova</t>
+          <t>Josyula</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -7981,12 +7973,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Andrey</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Prabhakar</t>
+          <t>Mayorov</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -7999,12 +7991,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Kishore</t>
+          <t>Ayan</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Josyula</t>
+          <t>Prabhakar</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -8017,15 +8009,19 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Andrey</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Mayorov</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr"/>
+          <t>Sawyer</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>billsawye@gmail.com</t>
+        </is>
+      </c>
       <c r="D406" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8035,15 +8031,19 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ayan</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Prabhakar</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr"/>
+          <t>Ding</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>jocyding@gmail.com</t>
+        </is>
+      </c>
       <c r="D407" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8053,19 +8053,15 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Sawyer</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>billsawye@gmail.com</t>
-        </is>
-      </c>
+          <t>Prabhakar</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8075,19 +8071,15 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Vito</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Ding</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>jocyding@gmail.com</t>
-        </is>
-      </c>
+          <t>Kwan</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8097,12 +8089,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Prabhakar</t>
+          <t>Kwan</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
@@ -8115,12 +8107,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Vito</t>
+          <t>Caeleb</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Kwan</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -8133,12 +8125,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Kwan</t>
+          <t>Groves</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
@@ -8151,12 +8143,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Caeleb</t>
+          <t>Adelene</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
@@ -8169,15 +8161,19 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>marco</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Groves</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr"/>
+          <t>Baldassarre</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>marco.baldassarre1@hotmail.com</t>
+        </is>
+      </c>
       <c r="D414" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8187,12 +8183,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Adelene</t>
+          <t>Anysia</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Mariyanayagam</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -8205,19 +8201,15 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>marco</t>
+          <t>Hon Wai</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Baldassarre</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>marco.baldassarre1@hotmail.com</t>
-        </is>
-      </c>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8227,12 +8219,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Anysia</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Mariyanayagam</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -8245,12 +8237,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Hon Wai</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Flynn</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -8263,12 +8255,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>Kin</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -8281,12 +8273,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>Jackie</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Flynn</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -8299,12 +8291,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Scarlett</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Kin</t>
+          <t>Flynn</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -8317,7 +8309,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Jackie</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -8335,12 +8327,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Scarlett</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Flynn</t>
+          <t>Nikolaidis</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
@@ -8353,12 +8345,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Almaria</t>
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
@@ -8371,15 +8363,19 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>noah</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Nikolaidis</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr"/>
+          <t>sotto</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>noahsotto@hotmail.com</t>
+        </is>
+      </c>
       <c r="D425" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8389,15 +8385,19 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Curci</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Almaria</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr"/>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>samantha.curci@yahoo.com</t>
+        </is>
+      </c>
       <c r="D426" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8407,19 +8407,15 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>noah</t>
+          <t>Sally</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>sotto</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>noahsotto@hotmail.com</t>
-        </is>
-      </c>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8429,17 +8425,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Curci</t>
+          <t>daniel</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>kosa</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>samantha.curci@yahoo.com</t>
+          <t>dankosa2003@hotmail.com</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -8451,12 +8447,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Sally</t>
+          <t>Kaia</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
@@ -8469,19 +8465,15 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>daniel</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>kosa</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>dankosa2003@hotmail.com</t>
-        </is>
-      </c>
+          <t>Kingston</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8491,12 +8483,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Kaia</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
@@ -8509,12 +8501,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Eilly</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Lau</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
@@ -8527,12 +8519,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Gopesh</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Srivastava</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
@@ -8545,12 +8537,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Eilly</t>
+          <t>Vickie</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Lau</t>
+          <t>Shum</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
@@ -8563,12 +8555,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Gopesh</t>
+          <t>Marie Helene</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Srivastava</t>
+          <t>Turgeon</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
@@ -8581,15 +8573,19 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Vickie</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Shum</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr"/>
+          <t>Tamburri</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>ltamburri05@gmail.com</t>
+        </is>
+      </c>
       <c r="D436" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8599,15 +8595,19 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Marie Helene</t>
+          <t>khim</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Turgeon</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr"/>
+          <t>hua</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>khimhua@yahoo.com</t>
+        </is>
+      </c>
       <c r="D437" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8617,17 +8617,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>david</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Tamburri</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>ltamburri05@gmail.com</t>
+          <t>trieudavid@yahoo.com</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -8637,19 +8637,11 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>khim</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>hua</t>
-        </is>
-      </c>
+      <c r="A439" t="inlineStr"/>
+      <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
-          <t>khimhua@yahoo.com</t>
+          <t>asif@pickleplex.ca</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -8661,19 +8653,15 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>david</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Trieu</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>trieudavid@yahoo.com</t>
-        </is>
-      </c>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8681,13 +8669,17 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr"/>
-      <c r="B441" t="inlineStr"/>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>asif@pickleplex.ca</t>
-        </is>
-      </c>
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>de Ridder</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8697,15 +8689,19 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>Ramisha</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Ho</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr"/>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>ramizainab73@gmail.com</t>
+        </is>
+      </c>
       <c r="D442" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8715,15 +8711,19 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>de Ridder</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr"/>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>critics.sashimi.0m@icloud.com</t>
+        </is>
+      </c>
       <c r="D443" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8733,17 +8733,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Ramisha</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>ramizainab73@gmail.com</t>
+          <t>jwong@mgp.ca</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -8755,19 +8755,15 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>critics.sashimi.0m@icloud.com</t>
-        </is>
-      </c>
+          <t>Tam</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8777,19 +8773,15 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>jwong@mgp.ca</t>
-        </is>
-      </c>
+          <t>Tam</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8799,7 +8791,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -8817,7 +8809,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Tobey</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -8835,12 +8827,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Tam</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -8853,12 +8845,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Tobey</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Tam</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -8871,15 +8863,19 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Debbie</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Liu</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr"/>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>dedbs03@hotmail.com</t>
+        </is>
+      </c>
       <c r="D451" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8889,15 +8885,19 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>DEFEI</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Nei</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr"/>
+          <t>wang</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>wmzhao05/@outlook.com</t>
+        </is>
+      </c>
       <c r="D452" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8907,19 +8907,15 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Debbie</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>dedbs03@hotmail.com</t>
-        </is>
-      </c>
+          <t>Hughes</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8929,19 +8925,15 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>DEFEI</t>
+          <t>Graham</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>wang</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>wmzhao05/@outlook.com</t>
-        </is>
-      </c>
+          <t>Hughes</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8951,15 +8943,19 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Hughes</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr"/>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>rentenwang28@gmail.com</t>
+        </is>
+      </c>
       <c r="D455" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -8969,12 +8965,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Graham</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Spadacini</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -8987,19 +8983,15 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Song</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>rentenwang28@gmail.com</t>
-        </is>
-      </c>
+          <t>Mcwlliams</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9009,12 +9001,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Spadacini</t>
+          <t>das</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -9027,12 +9019,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Mcwlliams</t>
+          <t>Spadacini</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -9045,12 +9037,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>das</t>
+          <t>Mcwlliams</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -9063,15 +9055,19 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Spadacini</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr"/>
+          <t>Iorio</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>chrisiorio@yahoo.com</t>
+        </is>
+      </c>
       <c r="D461" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9081,15 +9077,19 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>emily</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Mcwlliams</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr"/>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>chelseasmydog@gmail.com</t>
+        </is>
+      </c>
       <c r="D462" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9099,17 +9099,17 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>anthony</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Iorio</t>
+          <t>moschetti</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>chrisiorio@yahoo.com</t>
+          <t>amoschetti@rogers.com</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -9121,17 +9121,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>emily</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>chelseasmydog@gmail.com</t>
+          <t>paigeboston1@gmail.com</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -9143,17 +9143,17 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>anthony</t>
+          <t>jackson</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>moschetti</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>amoschetti@rogers.com</t>
+          <t>jacksonbeach27@gmail.com</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -9165,17 +9165,17 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>JF</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Ravenelle</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>paigeboston1@gmail.com</t>
+          <t>jraven_hot@hotmail.com</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -9187,17 +9187,17 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>jackson</t>
+          <t>sophia</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>boston</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>jacksonbeach27@gmail.com</t>
+          <t>sophiaboston14@gmail.com</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -9209,17 +9209,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>JF</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Ravenelle</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>jraven_hot@hotmail.com</t>
+          <t>tyboston61@gmail.com</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -9231,17 +9231,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>sophia</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>Foss</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>sophiaboston14@gmail.com</t>
+          <t>eric.c.foss@gmail.com</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -9253,17 +9253,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Moschetti</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>tyboston61@gmail.com</t>
+          <t>cmoschetti@rogers.com</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -9275,19 +9275,15 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Foss</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>eric.c.foss@gmail.com</t>
-        </is>
-      </c>
+          <t>Gorham</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9297,19 +9293,15 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Dominic</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Moschetti</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>cmoschetti@rogers.com</t>
-        </is>
-      </c>
+          <t>Gorham</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9319,15 +9311,19 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Gorham</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr"/>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>wwong@gmail.com</t>
+        </is>
+      </c>
       <c r="D473" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9337,12 +9333,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Dominic</t>
+          <t>JR</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Gorham</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
@@ -9355,7 +9351,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -9365,7 +9361,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>wwong@gmail.com</t>
+          <t>jennywongcanada@gmail.com</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -9377,12 +9373,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>JR</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
@@ -9395,19 +9391,15 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>jennywongcanada@gmail.com</t>
-        </is>
-      </c>
+          <t>Xu</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9417,12 +9409,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Johnny</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -9435,12 +9427,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -9453,7 +9445,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Johnny</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -9471,12 +9463,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -9489,12 +9481,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Jo</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Tse</t>
         </is>
       </c>
       <c r="C482" t="inlineStr"/>
@@ -9507,12 +9499,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Raymond</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C483" t="inlineStr"/>
@@ -9525,12 +9517,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Jo</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Tse</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -9543,12 +9535,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Raymond</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Chin</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -9561,12 +9553,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Hung</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
@@ -9579,12 +9571,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Chin</t>
+          <t>De Pina</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -9597,12 +9589,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Hung</t>
+          <t>Lau</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -9615,12 +9607,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Norah</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>De Pina</t>
+          <t>Rabinovich</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -9633,12 +9625,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Selma</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Lau</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -9651,12 +9643,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Norah</t>
+          <t>Ken</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Rabinovich</t>
+          <t>Lun</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -9669,12 +9661,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Selma</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Mandel</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -9687,12 +9679,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Ken</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Lun</t>
+          <t>Madel</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -9705,12 +9697,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mandel</t>
+          <t>Rabinovich</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -9723,12 +9715,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Madel</t>
+          <t>Kovarsky</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -9741,12 +9733,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Jo</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Rabinovich</t>
+          <t>Zee</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -9759,12 +9751,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Kovarsky</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -9777,12 +9769,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Jo</t>
+          <t>Wayne</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Zee</t>
+          <t>Cheu</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -9795,12 +9787,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -9813,7 +9805,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Wayne</t>
+          <t>Graydon</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -9831,12 +9823,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Graydon</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Cheu</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -9849,12 +9841,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Graydon</t>
+          <t>Bozena</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Cheu</t>
+          <t>Sankowska-Sasu</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
@@ -9867,12 +9859,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Graydon</t>
+          <t>Judy</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Cheu</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
@@ -9885,12 +9877,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Bozena</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Sankowska-Sasu</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
@@ -9903,15 +9895,19 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Judy</t>
+          <t>Clare</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr"/>
+          <t>Chui</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>coachclarec@gmail.com</t>
+        </is>
+      </c>
       <c r="D505" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9921,7 +9917,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -9939,19 +9935,15 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Clare</t>
+          <t>Amit</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Chui</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>coachclarec@gmail.com</t>
-        </is>
-      </c>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -9961,12 +9953,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Zayden</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
@@ -9979,12 +9971,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Amit</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
@@ -9997,15 +9989,19 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Zayden</t>
+          <t>lara</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr"/>
+          <t>de Waal</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>dewaallara@gmail.com</t>
+        </is>
+      </c>
       <c r="D510" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10015,12 +10011,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Doris</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Yeung</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
@@ -10033,17 +10029,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>lara</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>de Waal</t>
+          <t>pesegi1</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>dewaallara@gmail.com</t>
+          <t>helenpesegi2@gmail.com</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -10055,7 +10051,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Doris</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -10063,7 +10059,11 @@
           <t>Yeung</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>yhcaer2@gmail.com</t>
+        </is>
+      </c>
       <c r="D513" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10073,19 +10073,15 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Calvin</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>pesegi1</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>helenpesegi2@gmail.com</t>
-        </is>
-      </c>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10095,19 +10091,15 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Yeung</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>yhcaer2@gmail.com</t>
-        </is>
-      </c>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10117,15 +10109,19 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Calvin</t>
+          <t>helen</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr"/>
+          <t>pesegi</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>helenpesegi@gmail.com</t>
+        </is>
+      </c>
       <c r="D516" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10135,15 +10131,19 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>victoria</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Ho</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr"/>
+          <t>powell</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>victoriarochellepowell@gmail.com</t>
+        </is>
+      </c>
       <c r="D517" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10153,7 +10153,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>helen</t>
+          <t>luca</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>helenpesegi@gmail.com</t>
+          <t>helenpesegi1@gmail.com</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -10175,19 +10175,15 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>victoria</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>powell</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>victoriarochellepowell@gmail.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10197,17 +10193,17 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>luca</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>pesegi</t>
+          <t>Yeung</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>helenpesegi1@gmail.com</t>
+          <t>yhcaer1@gmail.com</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -10219,12 +10215,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Chi Ming</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Loo</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -10237,19 +10233,15 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Yeung</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>yhcaer1@gmail.com</t>
-        </is>
-      </c>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10259,12 +10251,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Chi Ming</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Loo</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -10277,15 +10269,19 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Toby</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr"/>
+          <t>Ts0</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>tobyy.tso@gmail.com</t>
+        </is>
+      </c>
       <c r="D524" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10295,12 +10291,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C525" t="inlineStr"/>
@@ -10313,19 +10309,15 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Toby</t>
+          <t>Cliff</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Ts0</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>tobyy.tso@gmail.com</t>
-        </is>
-      </c>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10335,12 +10327,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Kan</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
@@ -10353,15 +10345,19 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Cliff</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr"/>
+          <t>Colby</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>alexandracolby1@gmail.com</t>
+        </is>
+      </c>
       <c r="D528" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10371,15 +10367,19 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Kan</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Xie</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr"/>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>e_tvbox@outlook.com</t>
+        </is>
+      </c>
       <c r="D529" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10389,17 +10389,17 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Colby</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>alexandracolby1@gmail.com</t>
+          <t>unjc.email@gmail.com</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -10411,17 +10411,17 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>Rayson</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>ho</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>e_tvbox@outlook.com</t>
+          <t>raysonho@hotmail.com</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -10433,17 +10433,17 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Wes</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Sin</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>unjc.email@gmail.com</t>
+          <t>sinlokyin985@gmail.com</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -10455,19 +10455,15 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Rayson</t>
+          <t>Cal</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>ho</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>raysonho@hotmail.com</t>
-        </is>
-      </c>
+          <t>Thorne</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10477,19 +10473,15 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Wes</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Sin</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>sinlokyin985@gmail.com</t>
-        </is>
-      </c>
+          <t>Hammond</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10499,15 +10491,19 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Cal</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Thorne</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr"/>
+          <t>handwerker</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>ajhandwerker@yahoo.com</t>
+        </is>
+      </c>
       <c r="D535" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10517,15 +10513,19 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Hammond</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr"/>
+          <t>Nixon</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>jp_nixon2@hotmail.com</t>
+        </is>
+      </c>
       <c r="D536" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10535,17 +10535,17 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>handwerker</t>
+          <t>Foss</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>ajhandwerker@yahoo.com</t>
+          <t>jessica.foss10@gmail.com</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -10557,17 +10557,17 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>chi wai</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>sin</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>jp_nixon2@hotmail.com</t>
+          <t>mike666wes@gmail.com</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -10579,17 +10579,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>+Will</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Foss</t>
+          <t>Seguin</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>jessica.foss10@gmail.com</t>
+          <t>wseguin03@gmail.com</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -10601,17 +10601,17 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>chi wai</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>sin</t>
+          <t>Cheng</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>mike666wes@gmail.com</t>
+          <t>patrick-cheng@outlook.com</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -10623,17 +10623,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>+Will</t>
+          <t>john</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Seguin</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>wseguin03@gmail.com</t>
+          <t>johnlei01@gmail.com</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -10645,19 +10645,15 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Kingsley</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Cheng</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>patrick-cheng@outlook.com</t>
-        </is>
-      </c>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10667,19 +10663,15 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>Haylie</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>lei</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>johnlei01@gmail.com</t>
-        </is>
-      </c>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10689,12 +10681,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Kingsley</t>
+          <t>Kurtis</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -10707,12 +10699,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Haylie</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -10725,12 +10717,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Kurtis</t>
+          <t>Candy</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -10743,12 +10735,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Hussain</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
@@ -10761,12 +10753,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>Kenny KF</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
@@ -10779,12 +10771,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Darren</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Hussain</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
@@ -10797,12 +10789,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Kenny KF</t>
+          <t>Calvin</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -10815,12 +10807,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Darren</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Lui</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -10833,12 +10825,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Calvin</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Lui</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -10851,15 +10843,19 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Lui</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr"/>
+          <t>Dang</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>salinache@gmail.com</t>
+        </is>
+      </c>
       <c r="D553" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10869,12 +10865,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Lui</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -10887,19 +10883,15 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Dang</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>salinache@gmail.com</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10909,15 +10901,19 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Richmond Hill</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Domingo</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr"/>
+          <t>Pickleball Club</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>richmondhillpickleball@gmail.com</t>
+        </is>
+      </c>
       <c r="D556" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
@@ -10927,12 +10923,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Marwah</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -10943,19 +10939,11 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>Richmond Hill</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>Pickleball Club</t>
-        </is>
-      </c>
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>richmondhillpickleball@gmail.com</t>
+          <t>sofiapietrolungo@gmail.com</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -10967,12 +10955,12 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Marwah</t>
+          <t>Lijun</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Zhao</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -10983,50 +10971,18 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr"/>
-      <c r="B560" t="inlineStr"/>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>sofiapietrolungo@gmail.com</t>
-        </is>
-      </c>
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Hayden</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Muljo</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
-        <is>
-          <t>aurora@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>Lijun</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Zhao</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr"/>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>aurora@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>Hayden</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>Muljo</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr"/>
-      <c r="D562" t="inlineStr">
         <is>
           <t>aurora@pickleplex.ca</t>
         </is>
